--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-diagnosticreport-common.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-diagnosticreport-common.xlsx
@@ -272,7 +272,7 @@
     <t>患者、患者のグループ、デバイス、場所、これらから派生した検体に対して実行された診断的検査の結果と解釈。レポートには、依頼情報や依頼者情報などの臨床コンテキスト（文脈）、および１項目単位の結果、画像、テキストとコード化された解釈、および診断レポートのフォーマットされた表現のいくつかの組み合わせが含まれる。</t>
   </si>
   <si>
-    <t>これは単一のレポートをキャプチャすることを目的としており、複数のレポートをカバーする要約情報の表示に使用するのには適していない。たとえば、このリソースは、検査結果の累積レポート形式やシーケンスの詳細な構造化レポート用に作られていない。  
+    <t>これは単一のレポートを格納することを目的としており、複数のレポートを含む要約情報の表示に使用するのには適していない。たとえば、このリソースは、検査結果の累積レポート形式やシーケンスの詳細な構造化レポート用に作られていない。  
 【JP Core仕様】DiagnosticReportリソースの共通プロフィール</t>
   </si>
   <si>
@@ -491,7 +491,7 @@
     <t>実行者/実施者または他のシステムによって、この診断レポートに割り当てられた識別子</t>
   </si>
   <si>
-    <t>通常、診断サービスプロバイダの情報システム（フィラーID）によって割り当てられる。</t>
+    <t>通常、診断サービスを実施した施設の情報システム（実施者ID、HL7 v2 の filler ID）によって割り当てられる。</t>
   </si>
   <si>
     <t>発生源の検査室からこのレポートについてクエリを作成するとき、およびFHIRコンテキスト外のレポートにリンクするときに使用する識別子を知る必要がある。</t>
@@ -873,7 +873,7 @@
 </t>
   </si>
   <si>
-    <t>診断レポートが関係するヘルスケアイベントに関する情報</t>
+    <t>診断レポートが関係する診療イベントに関する情報</t>
   </si>
   <si>
     <t>受診、入院、診察など。通常、イベントが発生したEncounterであるが、一部のイベントは、Encounterの正式な完了の前または後に開始される場合があり、その場合でもEncounterのコンテキストに関連付けられている（例：入院前の臨床検査）。</t>
